--- a/tables/swan_loads.xlsx
+++ b/tables/swan_loads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C7052A-224E-C04F-A8AA-366204F66EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFAF1C3-C1A2-2F40-8107-9FEA48C3A8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9120" yWindow="5420" windowWidth="33880" windowHeight="17900" activeTab="1" xr2:uid="{F166D0B2-A6A5-A644-AFBB-9ACE97DF3A95}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
   <si>
     <t>YEAR</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>CATEGORY</t>
+  </si>
+  <si>
+    <t>ENTERING CSIEM DOMAIN</t>
+  </si>
+  <si>
+    <t>south-east (see Figure 7.22)</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1119,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>18</v>
@@ -1392,7 +1398,7 @@
         <v>23</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>25</v>
